--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460813</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>127460849</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460813</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>127460849</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,6 +1145,923 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127778114</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91786</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543549</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685968</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127776191</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91786</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>543565</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6685960</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127777680</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58494</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>543666</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6685794</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127776159</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543554</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6685967</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127776462</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>543634</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6685709</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127776456</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>543457</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6685779</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127774249</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Laxporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhodonia placenta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>543493</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6685980</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127776880</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>543646</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6685933</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127778103</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>543550</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6685968</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,48 +1244,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127776191</v>
+        <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91786</v>
+        <v>91338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543565</v>
+        <v>543634</v>
       </c>
       <c r="R7" t="n">
-        <v>6685960</v>
+        <v>6685709</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,19 +1312,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,60 +1329,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127777680</v>
+        <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>58494</v>
+        <v>91338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543666</v>
+        <v>543457</v>
       </c>
       <c r="R8" t="n">
-        <v>6685794</v>
+        <v>6685779</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,19 +1409,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,60 +1426,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127776159</v>
+        <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>91332</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543554</v>
+        <v>543493</v>
       </c>
       <c r="R9" t="n">
-        <v>6685967</v>
+        <v>6685980</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,49 +1509,40 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt, Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127776462</v>
+        <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543634</v>
+        <v>543550</v>
       </c>
       <c r="R10" t="n">
-        <v>6685709</v>
+        <v>6685968</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1662,48 +1636,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127776456</v>
+        <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>91792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543457</v>
+        <v>543565</v>
       </c>
       <c r="R11" t="n">
-        <v>6685779</v>
+        <v>6685960</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,80 +1707,88 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127774249</v>
+        <v>127777680</v>
       </c>
       <c r="B12" t="n">
-        <v>92060</v>
+        <v>58494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1105</v>
+        <v>208245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543493</v>
+        <v>543666</v>
       </c>
       <c r="R12" t="n">
-        <v>6685980</v>
+        <v>6685794</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,40 +1815,49 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127776880</v>
+        <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,19 +1883,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543646</v>
+        <v>543554</v>
       </c>
       <c r="R13" t="n">
-        <v>6685933</v>
+        <v>6685967</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,6 +1946,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1960,17 +1958,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127778103</v>
+        <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,17 +1996,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543550</v>
+        <v>543646</v>
       </c>
       <c r="R14" t="n">
-        <v>6685968</v>
+        <v>6685933</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2035,9 +2033,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,12 +2060,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460813</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>127460849</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92069</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
         <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127777680</v>
       </c>
       <c r="B12" t="n">
-        <v>58494</v>
+        <v>58497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
+          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
         <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127460813</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>127460849</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>92069</v>
+        <v>92077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
+          <t>Patric Engfeldt, Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
         <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127777680</v>
       </c>
       <c r="B12" t="n">
-        <v>58497</v>
+        <v>58503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Stig-Åke Svenson, Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
         <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>92077</v>
+        <v>92078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127460681</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>127460670</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127777680</v>
       </c>
       <c r="B12" t="n">
-        <v>58503</v>
+        <v>58504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>127778114</v>
       </c>
       <c r="B6" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127776462</v>
       </c>
       <c r="B7" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127776456</v>
       </c>
       <c r="B8" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127774249</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>127778103</v>
       </c>
       <c r="B10" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127776191</v>
       </c>
       <c r="B11" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127777680</v>
       </c>
       <c r="B12" t="n">
-        <v>58504</v>
+        <v>58516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127776159</v>
       </c>
       <c r="B13" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>127776880</v>
       </c>
       <c r="B14" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127460813</v>
+        <v>129575410</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>säter, Säter, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543475</v>
+        <v>543662</v>
       </c>
       <c r="R2" t="n">
-        <v>6685807</v>
+        <v>6685602</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -729,7 +725,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Säter</t>
+          <t>Hedemora</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -739,32 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Säter</t>
+          <t>Hedemora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök i Träd</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127460681</v>
+        <v>127774249</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>92662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,49 +783,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>säter, Säter, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543528</v>
+        <v>543493</v>
       </c>
       <c r="R3" t="n">
-        <v>6685963</v>
+        <v>6685980</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +861,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt, Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127460849</v>
+        <v>127773860</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,41 +884,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>säter, Säter, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543527</v>
+        <v>543492</v>
       </c>
       <c r="R4" t="n">
-        <v>6685843</v>
+        <v>6685995</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,27 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födohål.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,72 +958,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127460670</v>
+        <v>127773913</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>säter, Säter, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543539</v>
+        <v>543494</v>
       </c>
       <c r="R5" t="n">
-        <v>6685959</v>
+        <v>6685991</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,51 +1049,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778114</v>
+        <v>127773942</v>
       </c>
       <c r="B6" t="n">
-        <v>91906</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543549</v>
+        <v>543500</v>
       </c>
       <c r="R6" t="n">
-        <v>6685968</v>
+        <v>6685988</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1244,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127776462</v>
+        <v>127774283</v>
       </c>
       <c r="B7" t="n">
-        <v>91452</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543634</v>
+        <v>543516</v>
       </c>
       <c r="R7" t="n">
-        <v>6685709</v>
+        <v>6686000</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127776456</v>
+        <v>127776159</v>
       </c>
       <c r="B8" t="n">
-        <v>91452</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,19 +1290,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linsjön, Linsjön, Dlr</t>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543457</v>
+        <v>543554</v>
       </c>
       <c r="R8" t="n">
-        <v>6685779</v>
+        <v>6685967</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,77 +1332,85 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774249</v>
+        <v>127776456</v>
       </c>
       <c r="B9" t="n">
-        <v>92180</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543493</v>
+        <v>543457</v>
       </c>
       <c r="R9" t="n">
-        <v>6685980</v>
+        <v>6685779</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1520,7 +1451,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1532,17 +1462,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778103</v>
+        <v>127776462</v>
       </c>
       <c r="B10" t="n">
-        <v>91452</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543550</v>
+        <v>543634</v>
       </c>
       <c r="R10" t="n">
-        <v>6685968</v>
+        <v>6685709</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1636,51 +1566,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127776191</v>
+        <v>127776880</v>
       </c>
       <c r="B11" t="n">
-        <v>91906</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lertjärnen, Lertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543565</v>
+        <v>543646</v>
       </c>
       <c r="R11" t="n">
-        <v>6685960</v>
+        <v>6685933</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,7 +1636,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1646,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,7 +1655,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1747,48 +1673,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127777680</v>
+        <v>127778103</v>
       </c>
       <c r="B12" t="n">
-        <v>58516</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543666</v>
+        <v>543550</v>
       </c>
       <c r="R12" t="n">
-        <v>6685794</v>
+        <v>6685968</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,19 +1741,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,22 +1758,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127776159</v>
+        <v>127780329</v>
       </c>
       <c r="B13" t="n">
-        <v>91452</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,13 +1808,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543554</v>
+        <v>543485</v>
       </c>
       <c r="R13" t="n">
-        <v>6685967</v>
+        <v>6685997</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,7 +1843,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1853,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,10 +1881,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127776880</v>
+        <v>127773929</v>
       </c>
       <c r="B14" t="n">
-        <v>91452</v>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,37 +1892,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lertjärnen, Lertjärnen, Dlr</t>
+          <t>Linsjön, Linsjön, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543646</v>
+        <v>543504</v>
       </c>
       <c r="R14" t="n">
-        <v>6685933</v>
+        <v>6685984</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2033,19 +1949,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,15 +1966,1241 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127774230</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>543512</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6685999</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Cecilia Rastad</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127775979</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>543561</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6685969</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127776191</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>543565</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6685960</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127778114</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>543549</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6685968</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129575777</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Linsjön, Linsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>543666</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6685603</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127460813</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>säter, Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>543475</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6685807</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosök i Träd</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127460849</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>säter, Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>543527</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6685843</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födohål.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127777680</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lertjärnen, Lertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>543666</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6685794</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127460642</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>säter, Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>543561</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6685993</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127460670</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>säter, Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>543539</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6685959</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127460681</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>säter, Säter, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>543528</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6685963</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35411-2025 artfynd.xlsx
+++ b/artfynd/A 35411-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129575410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127773860</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127773913</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127773942</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774283</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776159</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776456</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776462</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776880</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778103</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1878,6 +1938,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127780329</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1975,6 +2040,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127773929</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774230</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775979</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776191</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127778114</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129575777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2618,6 +2713,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127460813</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2734,6 +2834,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127460849</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2841,6 +2946,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777680</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2961,6 +3071,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127460642</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3081,6 +3196,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127460670</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3201,8 +3321,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127460681</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>